--- a/testData/TC_Partner_Open_Quote.xlsx
+++ b/testData/TC_Partner_Open_Quote.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation_Project\E2E_Automation\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netapp-my.sharepoint.com/personal/sunilr2_netapp_com/Documents/Desktop/Playwright Python/E2E_Automation/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BDAB82-D813-480E-93BC-B6BE310EBF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{04BDAB82-D813-480E-93BC-B6BE310EBF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E12F1F39-E1C0-440E-9943-FA74ECE4493D}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,9 +45,6 @@
     <t>Quote Name</t>
   </si>
   <si>
-    <t>Quote 339352 for Accenture Ltd.</t>
-  </si>
-  <si>
     <t>LOGIN</t>
   </si>
   <si>
@@ -55,6 +52,9 @@
   </si>
   <si>
     <t>PARTNER PORTAL</t>
+  </si>
+  <si>
+    <t>Quote 710676 for Apple Inc.</t>
   </si>
 </sst>
 </file>
@@ -449,7 +449,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -457,11 +457,11 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="4"/>
     </row>
@@ -487,10 +487,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>339352</v>
+        <v>710676</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
